--- a/output/pdf_financials_xlsx/LIF.xlsx
+++ b/output/pdf_financials_xlsx/LIF.xlsx
@@ -1997,25 +1997,25 @@
         <v>6.203013</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>73.61188799999999</v>
+        <v>41.498184</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>26.923421</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>52.613924</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>34.955633</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>24.463512</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>23.937</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>40.498</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>82.913</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>39.904</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="35">
@@ -2089,25 +2089,25 @@
         <v>6.203013</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>73.61188799999999</v>
+        <v>41.498184</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>26.923421</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>52.613924</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>34.955633</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>24.463512</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>23.937</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>40.498</v>
+        <v>80.996</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>80.495</v>
@@ -2116,13 +2116,13 @@
         <v>77.85899999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>82.913</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>39.904</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>13.192</v>
       </c>
     </row>
     <row r="37">
@@ -2641,22 +2641,22 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>0.392173</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>30.053551</v>
+        <v>3.13013</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>52.613924</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>35.428259</v>
+        <v>0.472626</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>24.703811</v>
+        <v>0.240299</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>24.427</v>
+        <v>0.49</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
@@ -2668,13 +2668,13 @@
         <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>82.913</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>40.261</v>
+        <v>0.357</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>13.657</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="49">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
